--- a/hr_analytics_mini_project.xlsx
+++ b/hr_analytics_mini_project.xlsx
@@ -8,24 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ac0e23cc0feffb40/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55B65D6D-6482-4C11-91CB-E212E787E11C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="8_{55B65D6D-6482-4C11-91CB-E212E787E11C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FE99796-3AFA-4542-94DB-90BE12D467C2}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{D8B15532-CE68-4850-8FC4-1423AA62B539}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="1" xr2:uid="{D8B15532-CE68-4850-8FC4-1423AA62B539}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="4" r:id="rId2"/>
-    <sheet name="hr_analytics_mini_dataset" sheetId="1" r:id="rId3"/>
+    <sheet name="dashboard" sheetId="5" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId3"/>
+    <sheet name="hr_analytics_mini_dataset" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="53">
   <si>
     <t>EmployeeID</t>
   </si>
@@ -170,6 +171,21 @@
   <si>
     <t>Average of MonthlySalaryINR</t>
   </si>
+  <si>
+    <t>HR ANALYTICS DASHBOARD</t>
+  </si>
+  <si>
+    <t>TOTAL EMPLOYEES</t>
+  </si>
+  <si>
+    <t>ATTRITION RATE</t>
+  </si>
+  <si>
+    <t>EMPLOYEES LEFT</t>
+  </si>
+  <si>
+    <t>HIGHEST PAID DEPARTMENT</t>
+  </si>
 </sst>
 </file>
 
@@ -178,7 +194,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -313,8 +329,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -494,8 +524,20 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -610,6 +652,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -655,14 +712,25 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -791,7 +859,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-IN"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1289,7 +1357,1757 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[hr_analytics_mini_project.xlsx]Sheet1!PivotTable1</c:name>
+    <c:fmtId val="8"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Average Monthly Salary by Department</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-IN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-IN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Count of EmployeeID</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$4:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Finance</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>HR</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>IT</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Marketing</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$4:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9C22-48B1-A879-5F777B7B1EC4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Average of MonthlySalaryINR</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$4:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Finance</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>HR</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>IT</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Marketing</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$4:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>"₹"\ #,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>52800</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>37400</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>57000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>44333.333333333336</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>42285.714285714283</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9C22-48B1-A879-5F777B7B1EC4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="2108679152"/>
+        <c:axId val="1989269392"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="2108679152"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1989269392"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1989269392"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2108679152"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[hr_analytics_mini_project.xlsx]Sheet2!PivotTable2</c:name>
+    <c:fmtId val="5"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Employee Attrition (Yes vs No)</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-EAC4-4931-8475-33383143FD2F}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-EAC4-4931-8475-33383143FD2F}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$4:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>No</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Yes</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$4:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-EAC4-4931-8475-33383143FD2F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[hr_analytics_mini_project.xlsx]Sheet2!PivotTable2</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Employee Attrition (Yes vs No)</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$4:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>No</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Yes</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$4:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-16A8-48F5-94CA-362F884CFDCC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1832,6 +3650,1547 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -1853,6 +5212,128 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18F1E6DA-02AC-BBFB-BA72-40472929B2C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>99060</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A76EF9F1-70C3-4F37-A8A0-A12C7E1A0555}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{091F781E-ED2C-4E57-959F-3DA41B6E2824}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>6</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>571506</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F6897AA-4CEB-8BC9-D8D1-3469B4005DA5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2197,7 +5678,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BC3DEF59-74CD-40D4-8B37-3F0E995AFC64}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BC3DEF59-74CD-40D4-8B37-3F0E995AFC64}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
   <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField dataField="1" showAll="0"/>
@@ -2255,7 +5736,7 @@
     <dataField name="Count of EmployeeID" fld="0" subtotal="count" baseField="2" baseItem="0"/>
     <dataField name="Average of MonthlySalaryINR" fld="4" subtotal="average" baseField="2" baseItem="1" numFmtId="164"/>
   </dataFields>
-  <chartFormats count="2">
+  <chartFormats count="4">
     <chartFormat chart="1" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -2266,6 +5747,24 @@
       </pivotArea>
     </chartFormat>
     <chartFormat chart="1" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="5" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -2288,7 +5787,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A2C9C533-F5AB-432F-8102-AD4B0077A8AF}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A2C9C533-F5AB-432F-8102-AD4B0077A8AF}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField dataField="1" showAll="0"/>
@@ -2325,6 +5824,116 @@
   <dataFields count="1">
     <dataField name="Count of EmployeeID" fld="0" subtotal="count" baseField="6" baseItem="0"/>
   </dataFields>
+  <chartFormats count="10">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -2635,14 +6244,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E4976CA-8332-4F88-BB83-1DF16C53FFEA}">
   <dimension ref="A3:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>44</v>
       </c>
@@ -2653,69 +6262,69 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>5</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>52800</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>5</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>37400</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>7</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>57000</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <v>6</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>44333.333333333336</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <v>7</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <v>42285.714285714283</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9">
         <v>30</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>47066.666666666664</v>
       </c>
     </row>
@@ -2726,15 +6335,83 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C3D55FF-2B90-405F-8441-2B7CFF100448}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="22.8">
+      <c r="A1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" spans="1:8" ht="21">
+      <c r="A4" s="6">
+        <v>30</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="6">
+        <v>9</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42E598B1-DC7E-4083-AB38-46DF273D3D91}">
   <dimension ref="A3:B6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>44</v>
       </c>
@@ -2742,39 +6419,40 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D488275-22CC-440E-A186-4F6139ACC2C1}">
   <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
@@ -2783,7 +6461,7 @@
     <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2806,7 +6484,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>101</v>
       </c>
@@ -2829,7 +6507,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>102</v>
       </c>
@@ -2852,7 +6530,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>103</v>
       </c>
@@ -2875,7 +6553,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>104</v>
       </c>
@@ -2898,7 +6576,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>105</v>
       </c>
@@ -2921,7 +6599,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>106</v>
       </c>
@@ -2944,7 +6622,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>107</v>
       </c>
@@ -2967,7 +6645,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>108</v>
       </c>
@@ -2990,7 +6668,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>109</v>
       </c>
@@ -3013,7 +6691,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>110</v>
       </c>
@@ -3036,7 +6714,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>111</v>
       </c>
@@ -3059,7 +6737,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>112</v>
       </c>
@@ -3082,7 +6760,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>113</v>
       </c>
@@ -3105,7 +6783,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>114</v>
       </c>
@@ -3128,7 +6806,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>115</v>
       </c>
@@ -3151,7 +6829,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>116</v>
       </c>
@@ -3174,7 +6852,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>117</v>
       </c>
@@ -3197,7 +6875,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>118</v>
       </c>
@@ -3220,7 +6898,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>119</v>
       </c>
@@ -3243,7 +6921,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>120</v>
       </c>
@@ -3266,7 +6944,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>121</v>
       </c>
@@ -3289,7 +6967,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>122</v>
       </c>
@@ -3312,7 +6990,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>123</v>
       </c>
@@ -3335,7 +7013,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>124</v>
       </c>
@@ -3358,7 +7036,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>125</v>
       </c>
@@ -3381,7 +7059,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>126</v>
       </c>
@@ -3404,7 +7082,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>127</v>
       </c>
@@ -3427,7 +7105,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>128</v>
       </c>
@@ -3450,7 +7128,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>129</v>
       </c>
@@ -3473,7 +7151,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>130</v>
       </c>
